--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_253_R26.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_253_R26.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2247</v>
+        <v>5.2123</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8042</v>
+        <v>4.6881</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4206</v>
+        <v>0.5242</v>
       </c>
       <c r="G2" t="n">
-        <v>0.271</v>
+        <v>6.5759</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4049</v>
+        <v>1.7141</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6758999999999999</v>
+        <v>4.8618</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.494</v>
+        <v>5.4644</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.3872</v>
+        <v>0.7534</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8932</v>
+        <v>4.711</v>
       </c>
       <c r="M2" t="n">
-        <v>0.765</v>
+        <v>1.1115</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9823</v>
+        <v>0.9607</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2173</v>
+        <v>0.1507</v>
       </c>
       <c r="P2" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-2.5515</v>
+      </c>
+      <c r="R2" t="n">
         <v>2.3195</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.5515</v>
-      </c>
       <c r="S2" t="n">
-        <v>2.562</v>
+        <v>0.0824</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3857</v>
+        <v>-0.3692</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1763</v>
+        <v>0.4516</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W2" t="n">
         <v>2.1444</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0722</v>
+        <v>-3.3584</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.834</v>
+        <v>4.7239</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7131</v>
+        <v>1.5132</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1209</v>
+        <v>3.2107</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5759</v>
+        <v>0.271</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7141</v>
+        <v>-0.4049</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8618</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>5.4644</v>
+        <v>-0.494</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7534</v>
+        <v>-1.3872</v>
       </c>
       <c r="L3" t="n">
-        <v>4.711</v>
+        <v>0.8932</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1115</v>
+        <v>0.765</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9607</v>
+        <v>0.9823</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1507</v>
+        <v>-0.2173</v>
       </c>
       <c r="P3" t="n">
+        <v>2.3195</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-0.232</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-2.5515</v>
-      </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2959</v>
+        <v>1.0611</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3443</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0483</v>
+        <v>0.9665</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
         <v>2.1444</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.3584</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4657</v>
+        <v>3.4293</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0166</v>
+        <v>1.8121</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4491</v>
+        <v>1.6171</v>
       </c>
       <c r="G4" t="n">
         <v>2.2531</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2693</v>
+        <v>-0.3058</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1889</v>
+        <v>-0.0156</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4582</v>
+        <v>-0.2902</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1418</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6103</v>
+        <v>2.0702</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4684</v>
+        <v>-1.0084</v>
       </c>
       <c r="F5" t="n">
         <v>3.0787</v>
@@ -844,10 +844,10 @@
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2794</v>
+        <v>0.1806</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7073</v>
+        <v>-0.2473</v>
       </c>
       <c r="U5" t="n">
         <v>0.4279</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4162</v>
+        <v>1.6471</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4962</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9201</v>
+        <v>1.0881</v>
       </c>
       <c r="G6" t="n">
         <v>2.0746</v>
@@ -922,13 +922,13 @@
         <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9651</v>
+        <v>-0.7343</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2513</v>
+        <v>-0.1885</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7139</v>
+        <v>-0.5458</v>
       </c>
       <c r="V6" t="n">
         <v>1.4665</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>D. MUSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2016</v>
+        <v>0.3745</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0303</v>
+        <v>0.2811</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8287</v>
+        <v>0.0934</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0279</v>
+        <v>-0.3476</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8644</v>
+        <v>-1.067</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8365</v>
+        <v>0.7194</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3154</v>
+        <v>0.8609</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9913</v>
+        <v>-0.5476</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6758999999999999</v>
+        <v>1.4085</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2874</v>
+        <v>-1.2085</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1269</v>
+        <v>-0.5194</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1605</v>
+        <v>-0.6891</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3361</v>
+        <v>0.0442</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1968</v>
+        <v>0.134</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1393</v>
+        <v>-0.0898</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9304</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W7" t="n">
         <v>0.6778999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MUSA</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3133</v>
+        <v>0.3009</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1042</v>
+        <v>2.2976</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2091</v>
+        <v>-1.9967</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3476</v>
+        <v>1.0279</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.067</v>
+        <v>1.8644</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7194</v>
+        <v>-0.8365</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8609</v>
+        <v>2.3154</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5476</v>
+        <v>2.9913</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4085</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2085</v>
+        <v>-1.2874</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5194</v>
+        <v>-1.1269</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6891</v>
+        <v>-0.1605</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6435999999999999</v>
+        <v>0.4353</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2513</v>
+        <v>0.4641</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3923</v>
+        <v>-0.0288</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.9304</v>
       </c>
       <c r="W8" t="n">
         <v>0.6778999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6028</v>
+        <v>-0.4513</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6258</v>
+        <v>0.7438</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2286</v>
+        <v>-1.195</v>
       </c>
       <c r="G9" t="n">
         <v>0.8362000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1349</v>
+        <v>0.0167</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. CABOCLO</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7334</v>
+        <v>-1.397</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9432</v>
+        <v>-1.2489</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.6766</v>
+        <v>-0.1481</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2597</v>
+        <v>-1.4492</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6579</v>
+        <v>-0.3684</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3982</v>
+        <v>-1.0808</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6821</v>
+        <v>-1.0132</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3948</v>
+        <v>-0.6183</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7127</v>
+        <v>-0.3949</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4223</v>
+        <v>-0.436</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7369</v>
+        <v>0.2499</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3145</v>
+        <v>-0.6859</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9889</v>
+        <v>-0.2673</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3486</v>
+        <v>-0.2357</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3598</v>
+        <v>-0.0316</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.2862</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.3584</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>B. CABOCLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.96</v>
+        <v>-2.2731</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6775</v>
+        <v>1.2355</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2825</v>
+        <v>-3.5086</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4492</v>
+        <v>0.2597</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3684</v>
+        <v>0.6579</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0808</v>
+        <v>-0.3982</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0132</v>
+        <v>0.6821</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6183</v>
+        <v>1.3948</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3949</v>
+        <v>-0.7127</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.436</v>
+        <v>-0.4223</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2499</v>
+        <v>-0.7369</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6859</v>
+        <v>0.3145</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3917</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8303</v>
+        <v>0.4492</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6642</v>
+        <v>0.6409</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1661</v>
+        <v>-0.1918</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>-2.2862</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-3.3584</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.143</v>
+        <v>13.6368</v>
       </c>
       <c r="E12" t="n">
-        <v>9.379299999999999</v>
+        <v>10.8731</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7639</v>
+        <v>2.763799999999999</v>
       </c>
       <c r="G12" t="n">
         <v>11.5458</v>
@@ -1390,13 +1390,13 @@
         <v>15.0769</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5315000000000002</v>
+        <v>0.9621</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0984</v>
+        <v>0.3954000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5665999999999998</v>
+        <v>0.5667</v>
       </c>
       <c r="V12" t="n">
         <v>-0.03109999999999991</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2015</v>
+        <v>4.6625</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3362</v>
+        <v>2.808</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8652</v>
+        <v>1.8545</v>
       </c>
       <c r="G13" t="n">
         <v>2.3581</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2377</v>
+        <v>0.6987</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3734</v>
+        <v>0.0984</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6111</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0.6778999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>S. MCKISSIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3521</v>
+        <v>0.8905</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7492</v>
+        <v>1.7233</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3971</v>
+        <v>-0.8328</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1947</v>
+        <v>-0.6122</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3339</v>
+        <v>-1.1944</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5286</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3865</v>
+        <v>0.7139</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6504</v>
+        <v>-0.5007</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7361</v>
+        <v>1.2146</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.5812</v>
+        <v>-1.3261</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3165</v>
+        <v>-0.6938</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2647</v>
+        <v>-0.6323</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.232</v>
+        <v>0.232</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1009</v>
+        <v>0.1986</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2363</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8646</v>
+        <v>0.2614</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.0722</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2862</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. MCKISSIC</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5874</v>
+        <v>0.6622</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4874</v>
+        <v>3.3954</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9</v>
+        <v>-2.7332</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6122</v>
+        <v>-0.1947</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1944</v>
+        <v>0.3339</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5822000000000001</v>
+        <v>-0.5286</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7139</v>
+        <v>2.3865</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5007</v>
+        <v>1.6504</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2146</v>
+        <v>0.7361</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3261</v>
+        <v>-2.5812</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6938</v>
+        <v>-1.3165</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6323</v>
+        <v>-1.2647</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1046</v>
+        <v>0.411</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2987</v>
+        <v>-0.1175</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1942</v>
+        <v>0.5285</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>2.2862</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5779</v>
+        <v>0.5391</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9804</v>
+        <v>0.419</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.4025</v>
+        <v>0.1201</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4747</v>
+        <v>-1.3625</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4623</v>
+        <v>-0.2952</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9370000000000001</v>
+        <v>-1.0673</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2496</v>
+        <v>-0.5577</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.376</v>
+        <v>0.1918</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6257</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.225</v>
+        <v>-0.8048</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0862</v>
+        <v>-0.487</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3113</v>
+        <v>-0.3178</v>
       </c>
       <c r="P16" t="n">
         <v>1.8556</v>
@@ -1702,28 +1702,28 @@
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7863</v>
+        <v>0.1878</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9085</v>
+        <v>0.4406</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1221</v>
+        <v>-0.2528</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.5387</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>2.8223</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>-5.361</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0451</v>
+        <v>0.1454</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1831</v>
+        <v>3.3906</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.138</v>
+        <v>-3.2452</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3625</v>
+        <v>0.4747</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2952</v>
+        <v>-0.4623</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0673</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5577</v>
+        <v>0.2496</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1918</v>
+        <v>-0.376</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.6257</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8048</v>
+        <v>0.225</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.487</v>
+        <v>-0.0862</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3178</v>
+        <v>0.3113</v>
       </c>
       <c r="P17" t="n">
         <v>1.8556</v>
@@ -1780,28 +1780,28 @@
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3062</v>
+        <v>0.3539</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2047</v>
+        <v>0.3187</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5109</v>
+        <v>0.0351</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1418</v>
+        <v>-2.5387</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>2.8223</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-5.361</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2563</v>
+        <v>-0.7786</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4883</v>
+        <v>-1.9981</v>
       </c>
       <c r="F18" t="n">
+        <v>1.2195</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.4592</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1.1478</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.3114</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.7693</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.7255</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.0438</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.6899</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.4223</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.2676</v>
+      </c>
+      <c r="P18" t="n">
         <v>0.232</v>
       </c>
-      <c r="G18" t="n">
-        <v>0.2808</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-1.6865</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.9674</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.1819</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-1.3675</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2.5495</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-0.9011</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.319</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-0.5821</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-1.3917</v>
-      </c>
       <c r="Q18" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9268</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>1.809</v>
+        <v>-0.6051</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1177</v>
+        <v>0.5177</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6264</v>
+        <v>-1.0997</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5879</v>
+        <v>-1.6678</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9614</v>
+        <v>0.5681</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4592</v>
+        <v>0.2808</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1478</v>
+        <v>-1.6865</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3114</v>
+        <v>1.9674</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7693</v>
+        <v>1.1819</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7255</v>
+        <v>-1.3675</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0438</v>
+        <v>2.5495</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6899</v>
+        <v>-0.9011</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4223</v>
+        <v>-0.319</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2676</v>
+        <v>-0.5821</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9353</v>
+        <v>1.0833</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1949</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2596</v>
+        <v>0.4538</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1481</v>
+        <v>-3.5521</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6174</v>
+        <v>-1.8533</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5307</v>
+        <v>-1.6987</v>
       </c>
       <c r="G20" t="n">
         <v>-5.5291</v>
@@ -2014,13 +2014,13 @@
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0769</v>
+        <v>-0.3271</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0545</v>
+        <v>-0.2904</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1314</v>
+        <v>-0.0367</v>
       </c>
       <c r="V20" t="n">
         <v>1.6083</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. JOSEPH</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.4761</v>
+        <v>-5.9853</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.413</v>
+        <v>-5.214</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0631</v>
+        <v>-0.7713</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.493</v>
+        <v>-5.0087</v>
       </c>
       <c r="H21" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.1034</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5688</v>
+        <v>-4.9054</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9621</v>
+        <v>-3.2745</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1595</v>
+        <v>0.9417</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1975</v>
+        <v>-4.2162</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4551</v>
+        <v>-1.7342</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0838</v>
+        <v>-1.0451</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3713</v>
+        <v>-0.6891</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.9432</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.639</v>
+        <v>-3.4793</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0373</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1221</v>
+        <v>-0.7464</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1595</v>
+        <v>-0.0525</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0026</v>
+        <v>1.214</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>2.2862</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>C. JOSEPH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.4001</v>
+        <v>-6.8407</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.3935</v>
+        <v>-3.7669</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0066</v>
+        <v>-3.0738</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.0087</v>
+        <v>-0.493</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1034</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.9054</v>
+        <v>-0.5688</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.2745</v>
+        <v>0.9621</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9417</v>
+        <v>1.1595</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.2162</v>
+        <v>-0.1975</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7342</v>
+        <v>-1.4551</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0451</v>
+        <v>-1.0838</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6891</v>
+        <v>-0.3713</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3917</v>
+        <v>-3.9432</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4793</v>
+        <v>-4.639</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.2136</v>
+        <v>-0.402</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.9259</v>
+        <v>-0.2317</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2877</v>
+        <v>-0.1702</v>
       </c>
       <c r="V22" t="n">
-        <v>1.214</v>
+        <v>-2.0026</v>
       </c>
       <c r="W22" t="n">
-        <v>2.2862</v>
+        <v>0.1418</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-12.143</v>
+        <v>-11.3567</v>
       </c>
       <c r="E23" t="n">
         <v>-2.763799999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.3794</v>
+        <v>-8.5928</v>
       </c>
       <c r="G23" t="n">
         <v>-11.5458</v>
@@ -2218,16 +2218,16 @@
         <v>-7.3466</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.199299999999999</v>
+        <v>-4.1993</v>
       </c>
       <c r="J23" t="n">
         <v>0.2348999999999992</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3329999999999997</v>
+        <v>-0.3330000000000006</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5680000000000005</v>
+        <v>0.5680000000000003</v>
       </c>
       <c r="M23" t="n">
         <v>-11.7809</v>
@@ -2248,16 +2248,16 @@
         <v>13.9172</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5315999999999996</v>
+        <v>1.317899999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5668</v>
+        <v>-0.5667</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0984</v>
+        <v>1.8846</v>
       </c>
       <c r="V23" t="n">
-        <v>0.03109999999999991</v>
+        <v>0.03109999999999946</v>
       </c>
       <c r="W23" t="n">
         <v>12.645</v>
